--- a/assignments/wall/excels/remarks.xlsx
+++ b/assignments/wall/excels/remarks.xlsx
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10111</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P68" s="10" t="inlineStr">
         <is>
-          <t>00111</t>
+          <t>10111</t>
         </is>
       </c>
     </row>

--- a/assignments/wall/excels/remarks.xlsx
+++ b/assignments/wall/excels/remarks.xlsx
@@ -220,12 +220,12 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +500px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +500px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -245,7 +245,7 @@
     </comment>
     <comment ref="L5" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
@@ -275,12 +275,12 @@
     </comment>
     <comment ref="J9" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (00:00:02), -Chess (00:00:14), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +Brick (00:00:00), +Brick (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-DOCTYPE (00:00:02) ~0.00, -Chess (00:00:14) ~0.00, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.14, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +Brick (00:00:00), +Brick (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L9" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +35px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -gray (00:01:33) ~0.20, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +450px (00:00:00), +35px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D12" authorId="0" shapeId="0">
@@ -300,12 +300,12 @@
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L12" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +375px (00:00:00), +37px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.40, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +375px (00:00:00), +37px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D14" authorId="0" shapeId="0">
@@ -330,12 +330,12 @@
     </comment>
     <comment ref="J19" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -chess (00:02:38), -board (00:02:40), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -chess (00:02:38) ~0.00, -board (00:02:40) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L19" authorId="0" shapeId="0">
       <text>
-        <t>-chess (00:00:31), -board (00:00:33), -400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-chess (00:00:31) ~0.00, -board (00:00:33) ~0.20, -400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -350,12 +350,12 @@
     </comment>
     <comment ref="J21" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (00:00:02), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-DOCTYPE (00:00:02) ~0.00, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L21" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +height (00:00:00), +: (00:00:00), +425px (00:00:00), +; (00:00:00), +31px (00:00:00), +2px (00:00:00), +rgb (00:00:00), +( (00:00:00), +39 (00:00:00), +, (00:00:00), +35 (00:00:00), +, (00:00:00), +35 (00:00:00), +) (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -gray (00:01:33), -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +height (00:00:00), +: (00:00:00), +425px (00:00:00), +; (00:00:00), +31px (00:00:00), +2px (00:00:00), +rgb (00:00:00), +( (00:00:00), +39 (00:00:00), +, (00:00:00), +35 (00:00:00), +, (00:00:00), +35 (00:00:00), +) (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -375,7 +375,7 @@
     </comment>
     <comment ref="L24" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +29px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +5px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +29px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +5px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
@@ -400,7 +400,7 @@
     </comment>
     <comment ref="L25" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:05), -gray (00:01:33), -- (00:01:57), -color (00:01:58), -white (00:02:00), -- (00:02:07), -color (00:02:08), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +} (00:00:00), +425px (00:00:00), +height (00:00:00), +: (00:00:00), +240px (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +3px (00:00:00), +solid (00:00:00), +# (00:00:00), +333 (00:00:00), +; (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +# (00:00:00), +333 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +50px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +25px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:05) ~0.75, -gray (00:01:33) ~0.00, -- (00:01:57), -color (00:01:58), -white (00:02:00), -- (00:02:07), -color (00:02:08), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +} (00:00:00), +425px (00:00:00), +height (00:00:00), +: (00:00:00), +240px (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +3px (00:00:00), +solid (00:00:00), +# (00:00:00), +333 (00:00:00), +; (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +# (00:00:00), +333 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +50px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +25px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D28" authorId="0" shapeId="0">
@@ -455,7 +455,7 @@
     </comment>
     <comment ref="L30" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +20px (00:00:00), +3px (00:00:00), +grey (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.75, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +20px (00:00:00), +3px (00:00:00), +grey (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D31" authorId="0" shapeId="0">
@@ -480,7 +480,7 @@
     </comment>
     <comment ref="L31" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +26px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +71 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -white (00:02:00), -black (00:02:10), +425px (00:00:00), +26px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +71 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N31" authorId="0" shapeId="0">
@@ -510,7 +510,7 @@
     </comment>
     <comment ref="L36" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +# (00:00:00), +5a0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +. (00:00:00), +cell (00:00:00), +: (00:00:00), +nth (00:00:00), +- (00:00:00), +child (00:00:00), +( (00:00:00), +16n (00:00:00), ++ (00:00:00), +9 (00:00:00), +) (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +# (00:00:00), +5a0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +. (00:00:00), +cell (00:00:00), +: (00:00:00), +nth (00:00:00), +- (00:00:00), +child (00:00:00), +( (00:00:00), +16n (00:00:00), ++ (00:00:00), +9 (00:00:00), +) (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N36" authorId="0" shapeId="0">
@@ -535,7 +535,7 @@
     </comment>
     <comment ref="L41" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +430px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +• (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +430px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +• (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N41" authorId="0" shapeId="0">
@@ -560,12 +560,12 @@
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L42" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +# (00:00:00), +5a2c2c (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +# (00:00:00), +5a2c2c (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N42" authorId="0" shapeId="0">
@@ -585,12 +585,12 @@
     </comment>
     <comment ref="J45" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -chess (00:02:38), -board (00:02:40), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -chess (00:02:38) ~0.00, -board (00:02:40) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L45" authorId="0" shapeId="0">
       <text>
-        <t>-chess (00:00:31), -board (00:00:33), -400px (00:00:37), -50px (00:01:01), -white (00:02:00), -black (00:02:10), +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-chess (00:00:31) ~0.00, -board (00:00:33) ~0.20, -400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
@@ -610,7 +610,7 @@
     </comment>
     <comment ref="L46" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D47" authorId="0" shapeId="0">
@@ -635,7 +635,7 @@
     </comment>
     <comment ref="L47" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.14, +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N47" authorId="0" shapeId="0">
@@ -680,7 +680,7 @@
     </comment>
     <comment ref="L51" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:05), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +380px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +35px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:05) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +380px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +35px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N51" authorId="0" shapeId="0">
@@ -705,7 +705,7 @@
     </comment>
     <comment ref="L56" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +45px (00:00:00), +6px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +223 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +66 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +450px (00:00:00), +45px (00:00:00), +6px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +223 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +66 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N56" authorId="0" shapeId="0">
@@ -735,7 +735,7 @@
     </comment>
     <comment ref="L59" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +margin (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +margin (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N59" authorId="0" shapeId="0">
@@ -755,7 +755,7 @@
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -775,7 +775,7 @@
     </comment>
     <comment ref="L62" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +12 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +12 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -790,12 +790,12 @@
     </comment>
     <comment ref="J66" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:02:27), +Brick (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
+        <t>-Chess (00:02:27) ~0.00, +Brick (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L66" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -50px (00:01:05), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +51px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -50px (00:01:05) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +30px (00:00:00), +51px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
@@ -815,7 +815,7 @@
     </comment>
     <comment ref="L68" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -box (00:01:35), -- (00:01:36), -sizing (00:01:37), -: (00:01:38), -border (00:01:39), -- (00:01:40), -box (00:01:41), -; (00:01:42), -white (00:02:00), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +} (00:00:00), +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +228 (00:00:00), +, (00:00:00), +219 (00:00:00), +, (00:00:00), +219 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +21 (00:00:00), +, (00:00:00), +20 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.20, -box (00:01:35), -- (00:01:36), -sizing (00:01:37), -: (00:01:38), -border (00:01:39), -- (00:01:40), -box (00:01:41), -; (00:01:42), -white (00:02:00), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +} (00:00:00), +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +228 (00:00:00), +, (00:00:00), +219 (00:00:00), +, (00:00:00), +219 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +21 (00:00:00), +, (00:00:00), +20 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N68" authorId="0" shapeId="0">
@@ -845,7 +845,7 @@
     </comment>
     <comment ref="L70" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +430px (00:00:00), +30px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +2px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +430px (00:00:00), +30px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +2px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -860,12 +860,12 @@
     </comment>
     <comment ref="J71" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (00:00:00), -Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (00:00:00), -Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L71" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -white (00:02:00), -black (00:02:10), +435px (00:00:00), +20px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +435px (00:00:00), +20px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D72" authorId="0" shapeId="0">
@@ -890,12 +890,12 @@
     </comment>
     <comment ref="J73" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -chess (00:02:38), -board (00:02:40), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -chess (00:02:38) ~0.00, -board (00:02:40) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L73" authorId="0" shapeId="0">
       <text>
-        <t>-chess (00:00:31), -board (00:00:33), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +brick (00:00:00), +wall (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-chess (00:00:31) ~0.00, -board (00:00:33) ~0.20, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +brick (00:00:00), +wall (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -915,7 +915,7 @@
     </comment>
     <comment ref="L75" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -935,7 +935,7 @@
     </comment>
     <comment ref="L78" authorId="0" shapeId="0">
       <text>
-        <t>-50px (00:01:01), -white (00:02:00), -black (00:02:10), +35px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +235 (00:00:00), +, (00:00:00), +70 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +224 (00:00:00), +, (00:00:00), +68 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00)</t>
+        <t>-50px (00:01:01) ~0.50, -white (00:02:00), -black (00:02:10), +35px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +235 (00:00:00), +, (00:00:00), +70 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +224 (00:00:00), +, (00:00:00), +68 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N78" authorId="0" shapeId="0">
@@ -960,7 +960,7 @@
     </comment>
     <comment ref="L79" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +E2633C (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +E2633C (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -975,12 +975,12 @@
     </comment>
     <comment ref="J81" authorId="0" shapeId="0">
       <text>
-        <t>-W3Schools (00:17:42), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +W3schools (00:00:00)</t>
+        <t>-W3Schools (00:17:42) ~0.89, +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +W3schools (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L81" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +40px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +40px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E82" authorId="0" shapeId="0">
@@ -995,12 +995,12 @@
     </comment>
     <comment ref="J82" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +Wall (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +cursive (00:00:00), +; (00:00:00), +" (00:00:00), +" (00:00:00), +A (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +cursive (00:00:00), +; (00:00:00), +" (00:00:00), +" (00:00:00), +A (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L82" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +28px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +75px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.50, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +28px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +75px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D83" authorId="0" shapeId="0">
@@ -1020,12 +1020,12 @@
     </comment>
     <comment ref="J83" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L83" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ff0000 (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ff0000 (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N83" authorId="0" shapeId="0">
@@ -1050,12 +1050,12 @@
     </comment>
     <comment ref="J86" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L86" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +660000 (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +660000 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N86" authorId="0" shapeId="0">
@@ -1085,7 +1085,7 @@
     </comment>
     <comment ref="L87" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.14, +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N87" authorId="0" shapeId="0">
@@ -1115,7 +1115,7 @@
     </comment>
     <comment ref="L88" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +cd5c5c (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +cd5c5c (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N88" authorId="0" shapeId="0">
@@ -1125,7 +1125,7 @@
     </comment>
     <comment ref="D89" authorId="0" shapeId="0">
       <text>
-        <t>Student number not found, DOCX: cleared author metadata (answer-after-video-url.docx), DOCX: cleared author metadata (document.docx), DOCX error (~$swer-after-video-url.docx): Package not found at 'C:\UNIVERSITY\2026 - 2027\WebResearch\assignments\wall\students\opus 4.7\~$swer-after-video-url.docx'</t>
+        <t>Student number not found, DOCX: cleared author metadata (document.docx), DOCX error (~$swer-after-video-url.docx): Package not found at 'C:\UNIVERSITY\2026 - 2027\WebResearch\assignments\wall\students\opus 4.7\~$swer-after-video-url.docx'</t>
       </text>
     </comment>
     <comment ref="E89" authorId="0" shapeId="0">
@@ -1145,7 +1145,7 @@
     </comment>
     <comment ref="L89" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +28px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +e63946 (00:00:00), +# (00:00:00), +7d1620 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +28px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +e63946 (00:00:00), +# (00:00:00), +7d1620 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N89" authorId="0" shapeId="0">
@@ -1170,12 +1170,12 @@
     </comment>
     <comment ref="J90" authorId="0" shapeId="0">
       <text>
-        <t>-Chess (00:00:14), -Chess (00:02:27), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +br (00:00:00), +&gt; (00:00:00)</t>
+        <t>-Chess (00:00:14) ~0.00, -Chess (00:02:27) ~0.00, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +br (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="L90" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +30px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N90" authorId="0" shapeId="0">
@@ -1185,7 +1185,7 @@
     </comment>
     <comment ref="D91" authorId="0" shapeId="0">
       <text>
-        <t>Student number not found, Short name part(s) not auto-redacted (verify manually): v3, DOCX: cleared author metadata (answer.docx)</t>
+        <t>Student number not found, Short name part(s) not auto-redacted, DOCX: cleared author metadata (answer.docx)</t>
       </text>
     </comment>
     <comment ref="E91" authorId="0" shapeId="0">
@@ -1205,7 +1205,7 @@
     </comment>
     <comment ref="L91" authorId="0" shapeId="0">
       <text>
-        <t>-400px (00:00:37), +420px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +6b4c3b (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +&gt; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +4px (00:00:00), +4px (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +light (00:00:00), +, (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +inherit (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +7a4c2c (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-400px (00:00:37) ~0.80, +420px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +6b4c3b (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +&gt; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +4px (00:00:00), +4px (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +light (00:00:00), +, (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +inherit (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +7a4c2c (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N91" authorId="0" shapeId="0">
@@ -1235,7 +1235,7 @@
     </comment>
     <comment ref="L92" authorId="0" shapeId="0">
       <text>
-        <t>-50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +45px (00:00:00), +2px (00:00:00), +# (00:00:00), +444 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ffdddd (00:00:00), +# (00:00:00), +aa0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +45px (00:00:00), +2px (00:00:00), +# (00:00:00), +444 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ffdddd (00:00:00), +# (00:00:00), +aa0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="N92" authorId="0" shapeId="0">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +500px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +500px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-DOCTYPE (00:00:02), -Chess (00:00:14), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +Brick (00:00:00), +Brick (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-DOCTYPE (00:00:02) ~0.00, -Chess (00:00:14) ~0.00, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.14, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +Brick (00:00:00), +Brick (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +35px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -gray (00:01:33) ~0.20, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +450px (00:00:00), +35px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +- (00:00:00), +Wall (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +375px (00:00:00), +37px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.40, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +375px (00:00:00), +37px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -chess (00:02:38), -board (00:02:40), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -chess (00:02:38) ~0.00, -board (00:02:40) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-chess (00:00:31), -board (00:00:33), -400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-chess (00:00:31) ~0.00, -board (00:00:33) ~0.20, -400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-DOCTYPE (00:00:02), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-DOCTYPE (00:00:02) ~0.00, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +doctype (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +/ (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +height (00:00:00), +: (00:00:00), +425px (00:00:00), +; (00:00:00), +31px (00:00:00), +2px (00:00:00), +rgb (00:00:00), +( (00:00:00), +39 (00:00:00), +, (00:00:00), +35 (00:00:00), +, (00:00:00), +35 (00:00:00), +) (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -gray (00:01:33), -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +height (00:00:00), +: (00:00:00), +425px (00:00:00), +; (00:00:00), +31px (00:00:00), +2px (00:00:00), +rgb (00:00:00), +( (00:00:00), +39 (00:00:00), +, (00:00:00), +35 (00:00:00), +, (00:00:00), +35 (00:00:00), +) (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +29px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +5px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +29px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +5px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:05), -gray (00:01:33), -- (00:01:57), -color (00:01:58), -white (00:02:00), -- (00:02:07), -color (00:02:08), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +} (00:00:00), +425px (00:00:00), +height (00:00:00), +: (00:00:00), +240px (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +3px (00:00:00), +solid (00:00:00), +# (00:00:00), +333 (00:00:00), +; (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +# (00:00:00), +333 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +50px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +25px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:05) ~0.75, -gray (00:01:33) ~0.00, -- (00:01:57), -color (00:01:58), -white (00:02:00), -- (00:02:07), -color (00:02:08), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +} (00:00:00), +425px (00:00:00), +height (00:00:00), +: (00:00:00), +240px (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +3px (00:00:00), +solid (00:00:00), +# (00:00:00), +333 (00:00:00), +; (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +# (00:00:00), +333 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +50px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +0 (00:00:00), +0 (00:00:00), +25px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +13 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +20px (00:00:00), +3px (00:00:00), +grey (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.75, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +20px (00:00:00), +3px (00:00:00), +grey (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +26px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +71 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -white (00:02:00), -black (00:02:10), +425px (00:00:00), +26px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +71 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +# (00:00:00), +5a0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +. (00:00:00), +cell (00:00:00), +: (00:00:00), +nth (00:00:00), +- (00:00:00), +child (00:00:00), +( (00:00:00), +16n (00:00:00), ++ (00:00:00), +9 (00:00:00), +) (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +# (00:00:00), +5a0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +. (00:00:00), +cell (00:00:00), +: (00:00:00), +nth (00:00:00), +- (00:00:00), +child (00:00:00), +( (00:00:00), +16n (00:00:00), ++ (00:00:00), +9 (00:00:00), +) (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +430px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +• (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +430px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +• (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +# (00:00:00), +5a2c2c (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +# (00:00:00), +5a2c2c (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -chess (00:02:38), -board (00:02:40), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -chess (00:02:38) ~0.00, -board (00:02:40) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-chess (00:00:31), -board (00:00:33), -400px (00:00:37), -50px (00:01:01), -white (00:02:00), -black (00:02:10), +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-chess (00:00:31) ~0.00, -board (00:00:33) ~0.20, -400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +brick (00:00:00), +wall (00:00:00), +425px (00:00:00), +25px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.14, +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +width (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:05), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +380px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +35px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:05) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +380px (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +35px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +display (00:00:00), +: (00:00:00), +inline (00:00:00), +- (00:00:00), +block (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +45px (00:00:00), +6px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +223 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +66 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +450px (00:00:00), +45px (00:00:00), +6px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +223 (00:00:00), +, (00:00:00), +66 (00:00:00), +, (00:00:00), +66 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +margin (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +margin (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N59" s="6" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +12 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00), -black (00:02:10), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +1px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +234 (00:00:00), +, (00:00:00), +64 (00:00:00), +, (00:00:00), +12 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +173 (00:00:00), +, (00:00:00), +44 (00:00:00), +, (00:00:00), +5 (00:00:00), +) (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-Chess (00:02:27), +Brick (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
+          <t>-Chess (00:02:27) ~0.00, +Brick (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00)</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -50px (00:01:05), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +51px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -50px (00:01:05) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +30px (00:00:00), +51px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +ea420d (00:00:00), +# (00:00:00), +ad2c05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -box (00:01:35), -- (00:01:36), -sizing (00:01:37), -: (00:01:38), -border (00:01:39), -- (00:01:40), -box (00:01:41), -; (00:01:42), -white (00:02:00), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +} (00:00:00), +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +228 (00:00:00), +, (00:00:00), +219 (00:00:00), +, (00:00:00), +219 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +21 (00:00:00), +, (00:00:00), +20 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.20, -box (00:01:35), -- (00:01:36), -sizing (00:01:37), -: (00:01:38), -border (00:01:39), -- (00:01:40), -box (00:01:41), -; (00:01:42), -white (00:02:00), -black (00:02:10), +body (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +} (00:00:00), +450px (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +2px (00:00:00), +black (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +rgb (00:00:00), +( (00:00:00), +228 (00:00:00), +, (00:00:00), +219 (00:00:00), +, (00:00:00), +219 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +21 (00:00:00), +, (00:00:00), +20 (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +430px (00:00:00), +30px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +2px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +430px (00:00:00), +30px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +2px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>-&lt; (00:00:00), -Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (00:00:00), -Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -white (00:02:00), -black (00:02:10), +435px (00:00:00), +20px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +435px (00:00:00), +20px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +3px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -chess (00:02:38), -board (00:02:40), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -chess (00:02:38) ~0.00, -board (00:02:40) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +brick (00:00:00), +wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +row (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +a (00:00:00), +href (00:00:00), += (00:00:00), +" (00:00:00), +https (00:00:00), +: (00:00:00), +/ (00:00:00), +/ (00:00:00), +www (00:00:00), +. (00:00:00), +w3schools (00:00:00), +. (00:00:00), +com (00:00:00), +" (00:00:00), +target (00:00:00), += (00:00:00), +" (00:00:00), +_ (00:00:00), +blank (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Visit (00:00:00), +W3Schools (00:00:00), +. (00:00:00), +com (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +a (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-chess (00:00:31), -board (00:00:33), -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +brick (00:00:00), +wall (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-chess (00:00:31) ~0.00, -board (00:00:33) ~0.20, -display (00:00:39), -: (00:00:40), -flex (00:00:41), -; (00:00:42), -flex (00:00:43), -- (00:00:44), -wrap (00:00:45), -: (00:00:46), -wrap (00:00:47), -; (00:00:48), -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +brick (00:00:00), +wall (00:00:00), +. (00:00:00), +row (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +25px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>-50px (00:01:01), -white (00:02:00), -black (00:02:10), +35px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +235 (00:00:00), +, (00:00:00), +70 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +224 (00:00:00), +, (00:00:00), +68 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00)</t>
+          <t>-50px (00:01:01) ~0.50, -white (00:02:00), -black (00:02:10), +35px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +rgb (00:00:00), +( (00:00:00), +235 (00:00:00), +, (00:00:00), +70 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00), +rgb (00:00:00), +( (00:00:00), +224 (00:00:00), +, (00:00:00), +68 (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="N78" s="6" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +E2633C (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +25px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +E2633C (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>-W3Schools (00:17:42), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +W3schools (00:00:00)</t>
+          <t>-W3Schools (00:17:42) ~0.89, +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +W3schools (00:00:00)</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +40px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +40px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +3px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), +Brick (00:00:00), +Wall (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +cursive (00:00:00), +; (00:00:00), +" (00:00:00), +" (00:00:00), +A (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, +Brick (00:00:00), +Wall (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +cursive (00:00:00), +; (00:00:00), +" (00:00:00), +" (00:00:00), +A (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +432px (00:00:00), +28px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +75px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.50, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +432px (00:00:00), +28px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +5px (00:00:00), +; (00:00:00), +1 (00:00:00), +. (00:00:00), +75px (00:00:00), +# (00:00:00), +EA420D (00:00:00), +# (00:00:00), +AD2C05 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Board (00:00:15), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Board (00:00:15) ~0.20, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ff0000 (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ff0000 (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N83" s="6" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Chess (00:02:27), -Board (00:02:28), -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Chess (00:02:27) ~0.00, -Board (00:02:28) ~0.20, -&lt; (00:17:19), -a (00:17:20), -href (00:17:21), -= (00:17:22), -" (00:17:23), -https (00:17:24), -: (00:17:25), -/ (00:17:26), -/ (00:17:27), -www (00:17:28), -. (00:17:29), -w3schools (00:17:30), -. (00:17:31), -com (00:17:32), -" (00:17:33), -target (00:17:34), -= (00:17:35), -" (00:17:36), -_ (00:17:37), -blank (00:17:38), -" (00:17:39), -&gt; (00:17:40), -Visit (00:17:41), -W3Schools (00:17:42), -. (00:17:43), -com (00:17:44), -! (00:17:45), -&lt; (00:17:46), -/ (00:17:47), -a (00:17:48), -&gt; (00:17:49), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +Pattern (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +660000 (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +450px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +ff4d4d (00:00:00), +# (00:00:00), +660000 (00:00:00)</t>
         </is>
       </c>
       <c r="N86" s="6" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.14, +425px (00:00:00), +35px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +red (00:00:00), +darkred (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N87" s="6" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +cd5c5c (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.17, +425px (00:00:00), +30px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +# (00:00:00), +cd5c5c (00:00:00), +# (00:00:00), +8b0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N88" s="6" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +28px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +e63946 (00:00:00), +# (00:00:00), +7d1620 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +28px (00:00:00), +3px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +e63946 (00:00:00), +# (00:00:00), +7d1620 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N89" s="6" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>-Chess (00:00:14), -Chess (00:02:27), +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +br (00:00:00), +&gt; (00:00:00)</t>
+          <t>-Chess (00:00:14) ~0.00, -Chess (00:02:27) ~0.00, +Brick (00:00:00), +Wall (00:00:00), +Brick (00:00:00), +Wall (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +cell (00:00:00), +light (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +&lt; (00:00:00), +br (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), -50px (00:01:01), -1px (00:01:31), -white (00:02:00), -black (00:02:10), +425px (00:00:00), +30px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.60, -50px (00:01:01) ~0.75, -1px (00:01:31) ~0.67, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +425px (00:00:00), +30px (00:00:00), +2px (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N90" s="6" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>-400px (00:00:37), +420px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +6b4c3b (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +&gt; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +4px (00:00:00), +4px (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +light (00:00:00), +, (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +inherit (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +7a4c2c (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-400px (00:00:37) ~0.80, +420px (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f0f0f0 (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +1px (00:00:00), +solid (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +offset (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +left (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +6b4c3b (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00), +&gt; (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +40px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +6px (00:00:00), +4px (00:00:00), +4px (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +light (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +FF0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +8B0000 (00:00:00), +! (00:00:00), +important (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +light (00:00:00), +, (00:00:00), +. (00:00:00), +cell (00:00:00), +. (00:00:00), +dark (00:00:00), +{ (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +inherit (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +cell (00:00:00), +{ (00:00:00), +border (00:00:00), +: (00:00:00), +2px (00:00:00), +solid (00:00:00), +# (00:00:00), +7a4c2c (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +chess (00:00:00), +- (00:00:00), +board (00:00:00), +{ (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N91" s="6" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-50px (00:01:01), -1px (00:01:31), -gray (00:01:33), -white (00:02:00), -black (00:02:10), +45px (00:00:00), +2px (00:00:00), +# (00:00:00), +444 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ffdddd (00:00:00), +# (00:00:00), +aa0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-50px (00:01:01) ~0.50, -1px (00:01:31) ~0.67, -gray (00:01:33) ~0.00, -white (00:02:00) ~0.00, -black (00:02:10) ~0.00, +45px (00:00:00), +2px (00:00:00), +# (00:00:00), +444 (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +; (00:00:00), +# (00:00:00), +ffdddd (00:00:00), +# (00:00:00), +aa0000 (00:00:00), +. (00:00:00), +half (00:00:00), +- (00:00:00), +width (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="N92" s="6" t="inlineStr">
